--- a/outputs_xlsx_solution/test_new3.4-wide-NB-1.xlsx
+++ b/outputs_xlsx_solution/test_new3.4-wide-NB-1.xlsx
@@ -80,6 +80,9 @@
     <t>EX</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>fadd F4, F1, F1</t>
   </si>
   <si>
@@ -156,6 +159,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -699,7 +705,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -719,16 +725,16 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -748,16 +754,19 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -777,16 +786,22 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
       </c>
       <c r="I5" t="s">
         <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -809,10 +824,10 @@
         <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -832,7 +847,7 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" t="s">
         <v>14</v>
@@ -844,10 +859,10 @@
         <v>14</v>
       </c>
       <c r="K7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -867,7 +882,10 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="H8" t="s">
+        <v>15</v>
       </c>
       <c r="I8" t="s">
         <v>14</v>
@@ -879,19 +897,19 @@
         <v>14</v>
       </c>
       <c r="L8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -911,7 +929,7 @@
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P9" t="s">
         <v>14</v>
@@ -926,10 +944,10 @@
         <v>14</v>
       </c>
       <c r="T9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -940,17 +958,20 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" t="s">
         <v>15</v>
       </c>
-      <c r="F10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" t="s">
-        <v>20</v>
-      </c>
       <c r="J10" t="s">
         <v>14</v>
       </c>
@@ -961,22 +982,22 @@
         <v>14</v>
       </c>
       <c r="M10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -987,7 +1008,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -996,19 +1017,19 @@
         <v>9</v>
       </c>
       <c r="H11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q11" t="s">
         <v>14</v>
@@ -1020,10 +1041,10 @@
         <v>14</v>
       </c>
       <c r="T11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -1043,7 +1064,7 @@
         <v>9</v>
       </c>
       <c r="L12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U12" t="s">
         <v>14</v>
@@ -1058,13 +1079,13 @@
         <v>14</v>
       </c>
       <c r="Y12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -1075,7 +1096,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
@@ -1084,19 +1105,19 @@
         <v>9</v>
       </c>
       <c r="L13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T13" t="s">
         <v>14</v>
       </c>
       <c r="U13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="V13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -1107,7 +1128,7 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G14" t="s">
         <v>5</v>
@@ -1119,10 +1140,10 @@
         <v>14</v>
       </c>
       <c r="M14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -1133,7 +1154,7 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G15" t="s">
         <v>5</v>
@@ -1145,10 +1166,10 @@
         <v>14</v>
       </c>
       <c r="N15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -1159,7 +1180,7 @@
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G16" t="s">
         <v>5</v>
@@ -1168,16 +1189,16 @@
         <v>9</v>
       </c>
       <c r="M16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N16" t="s">
         <v>14</v>
       </c>
       <c r="O16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1188,7 +1209,7 @@
         <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G17" t="s">
         <v>5</v>
@@ -1197,16 +1218,16 @@
         <v>9</v>
       </c>
       <c r="M17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O17" t="s">
         <v>14</v>
       </c>
       <c r="P17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -1217,7 +1238,7 @@
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P18" t="s">
         <v>5</v>
@@ -1226,7 +1247,7 @@
         <v>9</v>
       </c>
       <c r="R18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T18" t="s">
         <v>14</v>
@@ -1238,19 +1259,19 @@
         <v>14</v>
       </c>
       <c r="W18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="X18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -1270,16 +1291,16 @@
         <v>9</v>
       </c>
       <c r="R19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="T19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA19" t="s">
         <v>14</v>
@@ -1294,13 +1315,13 @@
         <v>14</v>
       </c>
       <c r="AE19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -1311,7 +1332,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P20" t="s">
         <v>5</v>
@@ -1320,19 +1341,19 @@
         <v>9</v>
       </c>
       <c r="U20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z20" t="s">
         <v>14</v>
       </c>
       <c r="AA20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -1343,7 +1364,7 @@
         <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P21" t="s">
         <v>5</v>
@@ -1352,16 +1373,16 @@
         <v>9</v>
       </c>
       <c r="U21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V21" t="s">
         <v>14</v>
       </c>
       <c r="W21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -1372,7 +1393,7 @@
         <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q22" t="s">
         <v>5</v>
@@ -1381,16 +1402,19 @@
         <v>9</v>
       </c>
       <c r="U22" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="V22" t="s">
+        <v>15</v>
       </c>
       <c r="W22" t="s">
         <v>14</v>
       </c>
       <c r="X22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -1401,7 +1425,7 @@
         <v>56</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q23" t="s">
         <v>5</v>
@@ -1410,16 +1434,16 @@
         <v>9</v>
       </c>
       <c r="V23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X23" t="s">
         <v>14</v>
       </c>
       <c r="Y23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -1430,7 +1454,7 @@
         <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q24" t="s">
         <v>5</v>
@@ -1439,16 +1463,16 @@
         <v>9</v>
       </c>
       <c r="V24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y24" t="s">
         <v>14</v>
       </c>
       <c r="Z24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
@@ -1459,7 +1483,7 @@
         <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R25" t="s">
         <v>5</v>
@@ -1468,7 +1492,7 @@
         <v>9</v>
       </c>
       <c r="V25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z25" t="s">
         <v>14</v>
@@ -1480,19 +1504,19 @@
         <v>14</v>
       </c>
       <c r="AC25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AD25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -1512,22 +1536,22 @@
         <v>9</v>
       </c>
       <c r="V26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="W26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG26" t="s">
         <v>14</v>
@@ -1542,13 +1566,13 @@
         <v>14</v>
       </c>
       <c r="AK26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
@@ -1559,7 +1583,7 @@
         <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R27" t="s">
         <v>5</v>
@@ -1568,19 +1592,19 @@
         <v>9</v>
       </c>
       <c r="AA27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF27" t="s">
         <v>14</v>
       </c>
       <c r="AG27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
@@ -1591,7 +1615,7 @@
         <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R28" t="s">
         <v>5</v>
@@ -1600,16 +1624,16 @@
         <v>9</v>
       </c>
       <c r="AA28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB28" t="s">
         <v>14</v>
       </c>
       <c r="AC28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
@@ -1620,7 +1644,7 @@
         <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S29" t="s">
         <v>5</v>
@@ -1629,16 +1653,19 @@
         <v>9</v>
       </c>
       <c r="AA29" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>15</v>
       </c>
       <c r="AC29" t="s">
         <v>14</v>
       </c>
       <c r="AD29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
@@ -1649,7 +1676,7 @@
         <v>56</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S30" t="s">
         <v>5</v>
@@ -1658,16 +1685,16 @@
         <v>9</v>
       </c>
       <c r="AB30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD30" t="s">
         <v>14</v>
       </c>
       <c r="AE30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
@@ -1678,7 +1705,7 @@
         <v>60</v>
       </c>
       <c r="C31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S31" t="s">
         <v>5</v>
@@ -1687,16 +1714,16 @@
         <v>9</v>
       </c>
       <c r="AB31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE31" t="s">
         <v>14</v>
       </c>
       <c r="AF31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
@@ -1707,7 +1734,7 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T32" t="s">
         <v>5</v>
@@ -1716,7 +1743,7 @@
         <v>9</v>
       </c>
       <c r="AB32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF32" t="s">
         <v>14</v>
@@ -1728,19 +1755,19 @@
         <v>14</v>
       </c>
       <c r="AI32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
@@ -1760,22 +1787,22 @@
         <v>9</v>
       </c>
       <c r="AB33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AD33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM33" t="s">
         <v>14</v>
@@ -1790,13 +1817,13 @@
         <v>14</v>
       </c>
       <c r="AQ33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -1807,7 +1834,7 @@
         <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T34" t="s">
         <v>5</v>
@@ -1816,19 +1843,19 @@
         <v>9</v>
       </c>
       <c r="AG34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL34" t="s">
         <v>14</v>
       </c>
       <c r="AM34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AN34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
@@ -1839,7 +1866,7 @@
         <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T35" t="s">
         <v>5</v>
@@ -1848,16 +1875,16 @@
         <v>9</v>
       </c>
       <c r="AG35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH35" t="s">
         <v>14</v>
       </c>
       <c r="AI35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
@@ -1868,7 +1895,7 @@
         <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U36" t="s">
         <v>5</v>
@@ -1877,16 +1904,19 @@
         <v>9</v>
       </c>
       <c r="AG36" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="AH36" t="s">
+        <v>15</v>
       </c>
       <c r="AI36" t="s">
         <v>14</v>
       </c>
       <c r="AJ36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
@@ -1897,7 +1927,7 @@
         <v>56</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U37" t="s">
         <v>5</v>
@@ -1906,16 +1936,16 @@
         <v>9</v>
       </c>
       <c r="AH37" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ37" t="s">
         <v>14</v>
       </c>
       <c r="AK37" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
@@ -1926,7 +1956,7 @@
         <v>60</v>
       </c>
       <c r="C38" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U38" t="s">
         <v>5</v>
@@ -1935,16 +1965,16 @@
         <v>9</v>
       </c>
       <c r="AH38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK38" t="s">
         <v>14</v>
       </c>
       <c r="AL38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT38" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39">
@@ -1955,7 +1985,7 @@
         <v>36</v>
       </c>
       <c r="C39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V39" t="s">
         <v>5</v>
@@ -1964,7 +1994,7 @@
         <v>9</v>
       </c>
       <c r="AH39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL39" t="s">
         <v>14</v>
@@ -1976,19 +2006,19 @@
         <v>14</v>
       </c>
       <c r="AO39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
@@ -2008,22 +2038,22 @@
         <v>9</v>
       </c>
       <c r="AH40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS40" t="s">
         <v>14</v>
@@ -2038,10 +2068,10 @@
         <v>14</v>
       </c>
       <c r="AW40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
@@ -2052,7 +2082,7 @@
         <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V41" t="s">
         <v>5</v>
@@ -2061,19 +2091,19 @@
         <v>9</v>
       </c>
       <c r="AM41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR41" t="s">
         <v>14</v>
       </c>
       <c r="AS41" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT41" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX41" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
@@ -2084,7 +2114,7 @@
         <v>48</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V42" t="s">
         <v>5</v>
@@ -2093,16 +2123,16 @@
         <v>9</v>
       </c>
       <c r="AM42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN42" t="s">
         <v>14</v>
       </c>
       <c r="AO42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX42" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
@@ -2113,7 +2143,7 @@
         <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W43" t="s">
         <v>5</v>
@@ -2122,16 +2152,19 @@
         <v>9</v>
       </c>
       <c r="AM43" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="AN43" t="s">
+        <v>15</v>
       </c>
       <c r="AO43" t="s">
         <v>14</v>
       </c>
       <c r="AP43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44">
@@ -2142,7 +2175,7 @@
         <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W44" t="s">
         <v>5</v>
@@ -2151,16 +2184,16 @@
         <v>9</v>
       </c>
       <c r="AN44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP44" t="s">
         <v>14</v>
       </c>
       <c r="AQ44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY44" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45">
@@ -2171,7 +2204,7 @@
         <v>60</v>
       </c>
       <c r="C45" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="W45" t="s">
         <v>5</v>
@@ -2180,16 +2213,16 @@
         <v>9</v>
       </c>
       <c r="AN45" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ45" t="s">
         <v>14</v>
       </c>
       <c r="AR45" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY45" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
@@ -2200,7 +2233,7 @@
         <v>64</v>
       </c>
       <c r="C46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR46" t="s">
         <v>5</v>
@@ -2218,10 +2251,10 @@
         <v>14</v>
       </c>
       <c r="AW46" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
@@ -2241,7 +2274,7 @@
         <v>9</v>
       </c>
       <c r="AT47" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX47" t="s">
         <v>14</v>
@@ -2256,7 +2289,7 @@
         <v>14</v>
       </c>
       <c r="BB47" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
@@ -2267,7 +2300,7 @@
         <v>72</v>
       </c>
       <c r="C48" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR48" t="s">
         <v>5</v>
@@ -2276,19 +2309,19 @@
         <v>9</v>
       </c>
       <c r="AT48" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW48" t="s">
         <v>14</v>
       </c>
       <c r="AX48" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49">
@@ -2299,7 +2332,7 @@
         <v>76</v>
       </c>
       <c r="C49" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR49" t="s">
         <v>5</v>
@@ -2308,18 +2341,18 @@
         <v>9</v>
       </c>
       <c r="AT49" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB49" t="s">
         <v>14</v>
       </c>
       <c r="BC49" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52">
@@ -2327,7 +2360,7 @@
         <v>5</v>
       </c>
       <c r="B52" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53">
@@ -2335,15 +2368,15 @@
         <v>9</v>
       </c>
       <c r="B53" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55">
@@ -2351,39 +2384,55 @@
         <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B56" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B58" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B59" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>26</v>
+      </c>
+      <c r="B60" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
